--- a/data/past_vendor_data.xlsx
+++ b/data/past_vendor_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manisha\Desktop\ProcurementSystem\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BD13201-38EC-4E8A-A7DF-4A02B1B0E5BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0B12C07-28E4-403A-9DFB-2DBF2437502F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{85E520B3-4265-4A8F-A447-417C75FFD803}"/>
   </bookViews>
